--- a/data/insert_data2.xlsx
+++ b/data/insert_data2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongh\Desktop\DATN\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C875133-221A-4E85-858E-80E813E64581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56647561-1A66-483E-8DBB-9CD99F09AB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3D981FB0-44E2-41B7-9F67-DB59F3D45F24}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3D981FB0-44E2-41B7-9F67-DB59F3D45F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,165 +74,81 @@
     <t>Lê Hồng Dũng</t>
   </si>
   <si>
-    <t>184 XYZ Road</t>
-  </si>
-  <si>
     <t>Đặng Văn An</t>
   </si>
   <si>
-    <t>24 XYZ Road</t>
-  </si>
-  <si>
     <t>Đặng Minh Dũng</t>
   </si>
   <si>
-    <t>45 XYZ Road</t>
-  </si>
-  <si>
     <t>Trần Minh Linh</t>
   </si>
   <si>
-    <t>115 XYZ Road</t>
-  </si>
-  <si>
     <t>Đặng Thị Linh</t>
   </si>
   <si>
-    <t>182 XYZ Road</t>
-  </si>
-  <si>
     <t>Hoàng Thị Khánh</t>
   </si>
   <si>
-    <t>18 XYZ Road</t>
-  </si>
-  <si>
     <t>Nguyễn Thuỳ Dũng</t>
   </si>
   <si>
-    <t>130 XYZ Road</t>
-  </si>
-  <si>
     <t>Phạm Bảo Linh</t>
   </si>
   <si>
-    <t>84 XYZ Road</t>
-  </si>
-  <si>
     <t>Hoàng Văn An</t>
   </si>
   <si>
-    <t>193 XYZ Road</t>
-  </si>
-  <si>
     <t>Võ Văn Linh</t>
   </si>
   <si>
-    <t>150 XYZ Road</t>
-  </si>
-  <si>
     <t>Lê Hữu Bình</t>
   </si>
   <si>
-    <t>140 XYZ Road</t>
-  </si>
-  <si>
     <t>Huỳnh Thị An</t>
   </si>
   <si>
-    <t>194 XYZ Road</t>
-  </si>
-  <si>
     <t>Đặng Bảo Tùng</t>
   </si>
   <si>
-    <t>165 XYZ Road</t>
-  </si>
-  <si>
     <t>Phạm Hồng Hạnh</t>
   </si>
   <si>
-    <t>43 XYZ Road</t>
-  </si>
-  <si>
     <t>Phạm Tuấn Chi</t>
   </si>
   <si>
-    <t>55 XYZ Road</t>
-  </si>
-  <si>
-    <t>62 XYZ Road</t>
-  </si>
-  <si>
     <t>Lê Hồng Linh</t>
   </si>
   <si>
-    <t>27 XYZ Road</t>
-  </si>
-  <si>
     <t>Trần Hữu Khánh</t>
   </si>
   <si>
-    <t>171 XYZ Road</t>
-  </si>
-  <si>
     <t>Nguyễn Thuỳ Chi</t>
   </si>
   <si>
-    <t>110 XYZ Road</t>
-  </si>
-  <si>
     <t>Trần Bảo Linh</t>
   </si>
   <si>
-    <t>77 XYZ Road</t>
-  </si>
-  <si>
     <t>Võ Hồng Dũng</t>
   </si>
   <si>
-    <t>58 XYZ Road</t>
-  </si>
-  <si>
     <t>Hoàng Bảo Hạnh</t>
   </si>
   <si>
-    <t>180 XYZ Road</t>
-  </si>
-  <si>
     <t>Hoàng Minh Linh</t>
   </si>
   <si>
-    <t>151 XYZ Road</t>
-  </si>
-  <si>
     <t>Lê Văn Tùng</t>
   </si>
   <si>
-    <t>15 XYZ Road</t>
-  </si>
-  <si>
     <t>Phạm Thuỳ Dũng</t>
   </si>
   <si>
-    <t>48 XYZ Road</t>
-  </si>
-  <si>
     <t>Nguyễn Minh Linh</t>
   </si>
   <si>
-    <t>116 XYZ Road</t>
-  </si>
-  <si>
-    <t>79 XYZ Road</t>
-  </si>
-  <si>
     <t>Đặng Thuỳ Dũng</t>
   </si>
   <si>
-    <t>86 XYZ Road</t>
-  </si>
-  <si>
     <t>123456</t>
   </si>
   <si>
@@ -327,6 +243,90 @@
   </si>
   <si>
     <t>Information Technology 30</t>
+  </si>
+  <si>
+    <t>5 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>6 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>7 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>8 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>9 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>10 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>11 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>12 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>13 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>14 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>15 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>16 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>17 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>18 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>19 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>20 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>21 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>22 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>23 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>24 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>25 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>26 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>27 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>28 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>29 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>30 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>31 Dương Văn Dương</t>
+  </si>
+  <si>
+    <t>32 Dương Văn Dương</t>
   </si>
 </sst>
 </file>
@@ -770,19 +770,19 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2001215829</v>
+        <v>2001215828</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -791,13 +791,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -809,17 +809,17 @@
         <v>11</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
+      <c r="D4" t="s">
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -828,20 +828,20 @@
         <v>2001215822</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
+      <c r="D5" t="s">
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -850,20 +850,20 @@
         <v>2001215899</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
+      <c r="D6" t="s">
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -872,20 +872,20 @@
         <v>2001215868</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
+      <c r="D7" t="s">
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -894,20 +894,20 @@
         <v>2001215853</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
+      <c r="D8" t="s">
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -916,20 +916,20 @@
         <v>2001215823</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
+      <c r="D9" t="s">
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J9" s="4"/>
     </row>
@@ -938,20 +938,20 @@
         <v>2001215904</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
+      <c r="D10" t="s">
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -960,20 +960,20 @@
         <v>2001215944</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>26</v>
+      <c r="D11" t="s">
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -982,20 +982,20 @@
         <v>2001215812</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
+      <c r="D12" t="s">
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -1004,20 +1004,20 @@
         <v>2001215962</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>30</v>
+      <c r="D13" t="s">
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J13" s="4"/>
     </row>
@@ -1026,20 +1026,20 @@
         <v>2001215912</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>32</v>
+      <c r="D14" t="s">
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J14" s="4"/>
     </row>
@@ -1048,20 +1048,20 @@
         <v>2001215944</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
+      <c r="D15" t="s">
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J15" s="4"/>
     </row>
@@ -1070,20 +1070,20 @@
         <v>2001215976</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
+      <c r="D16" t="s">
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J16" s="4"/>
     </row>
@@ -1092,20 +1092,20 @@
         <v>2001215927</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>38</v>
+      <c r="D17" t="s">
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J17" s="4"/>
     </row>
@@ -1114,20 +1114,20 @@
         <v>2001215904</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>40</v>
+      <c r="D18" t="s">
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J18" s="4"/>
     </row>
@@ -1136,20 +1136,20 @@
         <v>2001215812</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
+      <c r="D19" t="s">
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J19" s="4"/>
     </row>
@@ -1158,20 +1158,20 @@
         <v>2001215880</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>43</v>
+      <c r="D20" t="s">
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J20" s="4"/>
     </row>
@@ -1180,20 +1180,20 @@
         <v>2001215946</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>45</v>
+      <c r="D21" t="s">
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J21" s="4"/>
     </row>
@@ -1202,20 +1202,20 @@
         <v>2001215908</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>47</v>
+      <c r="D22" t="s">
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J22" s="4"/>
     </row>
@@ -1224,20 +1224,20 @@
         <v>2001215810</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
-        <v>49</v>
+      <c r="D23" t="s">
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J23" s="4"/>
     </row>
@@ -1246,20 +1246,20 @@
         <v>2001215857</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
-        <v>51</v>
+      <c r="D24" t="s">
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J24" s="4"/>
     </row>
@@ -1268,20 +1268,20 @@
         <v>2001215843</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
-        <v>53</v>
+      <c r="D25" t="s">
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J25" s="4"/>
     </row>
@@ -1290,20 +1290,20 @@
         <v>2001215817</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
-        <v>55</v>
+      <c r="D26" t="s">
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J26" s="4"/>
     </row>
@@ -1312,20 +1312,20 @@
         <v>2001215966</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
+      <c r="D27" t="s">
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J27" s="4"/>
     </row>
@@ -1334,20 +1334,20 @@
         <v>2001215929</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
-        <v>59</v>
+      <c r="D28" t="s">
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J28" s="4"/>
     </row>
@@ -1356,20 +1356,20 @@
         <v>2001215983</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
-        <v>61</v>
+      <c r="D29" t="s">
+        <v>94</v>
       </c>
       <c r="E29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" t="s">
         <v>66</v>
       </c>
-      <c r="F29" t="s">
-        <v>94</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J29" s="4"/>
     </row>
@@ -1378,20 +1378,20 @@
         <v>2001215801</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
-        <v>62</v>
+      <c r="D30" t="s">
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -1400,20 +1400,20 @@
         <v>2001215922</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
-        <v>64</v>
+      <c r="D31" t="s">
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J31" s="4"/>
     </row>
